--- a/data/League of Amazing Programmers Inventory.xlsx
+++ b/data/League of Amazing Programmers Inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Proj/proj/league-projects/infrastructure/inventory/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2843B38E-C8E6-9545-ABC1-10FF279E4634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8641FB06-2EAA-4D43-A495-6842586370B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13440" yWindow="4120" windowWidth="37760" windowHeight="24680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1340" yWindow="1560" windowWidth="37760" windowHeight="24680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LIST OF ASSETS" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="687">
   <si>
     <t>Scrapped</t>
   </si>
@@ -807,9 +807,6 @@
     <t>66ZZ6F2</t>
   </si>
   <si>
-    <t>WTS PC 36</t>
-  </si>
-  <si>
     <t>BW</t>
   </si>
   <si>
@@ -2122,6 +2119,9 @@
   </si>
   <si>
     <t>Sarah's Hard Drive</t>
+  </si>
+  <si>
+    <t>Host Name</t>
   </si>
 </sst>
 </file>
@@ -2145,108 +2145,127 @@
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2257,6 +2276,7 @@
       <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2268,6 +2288,7 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2278,53 +2299,62 @@
       <strike/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="13">
@@ -2443,7 +2473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2610,14 +2640,8 @@
     <xf numFmtId="164" fontId="17" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="22" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="22" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2627,22 +2651,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2667,13 +2675,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Bags-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3108,7 +3132,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>686</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -4603,7 +4627,7 @@
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E30" s="14">
         <v>8</v>
@@ -4653,7 +4677,7 @@
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E31" s="14">
         <v>8</v>
@@ -4703,7 +4727,7 @@
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E32" s="14">
         <v>8</v>
@@ -4753,7 +4777,7 @@
       </c>
       <c r="C33" s="14"/>
       <c r="D33" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E33" s="14">
         <v>8</v>
@@ -4803,7 +4827,7 @@
       </c>
       <c r="C34" s="14"/>
       <c r="D34" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E34" s="14">
         <v>8</v>
@@ -4853,7 +4877,7 @@
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E35" s="14">
         <v>8</v>
@@ -4903,7 +4927,7 @@
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E36" s="14">
         <v>10</v>
@@ -4955,7 +4979,7 @@
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E37" s="14">
         <v>10</v>
@@ -5007,7 +5031,7 @@
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E38" s="14">
         <v>8</v>
@@ -5059,7 +5083,7 @@
       </c>
       <c r="C39" s="14"/>
       <c r="D39" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E39" s="14">
         <v>10</v>
@@ -5109,7 +5133,7 @@
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E40" s="14">
         <v>10</v>
@@ -5525,7 +5549,7 @@
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>220</v>
@@ -5575,7 +5599,7 @@
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E58" s="14" t="s">
         <v>220</v>
@@ -5625,7 +5649,7 @@
       </c>
       <c r="C59" s="14"/>
       <c r="D59" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>220</v>
@@ -5675,7 +5699,7 @@
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>230</v>
@@ -5727,7 +5751,7 @@
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>230</v>
@@ -5779,7 +5803,7 @@
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E62" s="14" t="s">
         <v>230</v>
@@ -5834,7 +5858,9 @@
         <v>242</v>
       </c>
       <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
+      <c r="F63" s="22" t="s">
+        <v>242</v>
+      </c>
       <c r="G63" s="22" t="s">
         <v>243</v>
       </c>
@@ -5879,29 +5905,29 @@
         <v>247</v>
       </c>
       <c r="D64" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="F64" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>250</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J64" s="7" t="s">
         <v>251</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="K64" s="8">
         <v>42949</v>
       </c>
       <c r="L64" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M64" s="8">
         <v>45406</v>
@@ -5927,25 +5953,27 @@
     <row r="65" spans="1:30" ht="13">
       <c r="A65" s="22"/>
       <c r="B65" s="23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C65" s="25"/>
       <c r="D65" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="G65" s="22" t="s">
         <v>255</v>
-      </c>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22" t="s">
-        <v>256</v>
       </c>
       <c r="H65" s="25">
         <v>113</v>
       </c>
       <c r="I65" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="J65" s="28" t="s">
         <v>257</v>
-      </c>
-      <c r="J65" s="28" t="s">
-        <v>258</v>
       </c>
       <c r="K65" s="25"/>
       <c r="L65" s="25"/>
@@ -5973,25 +6001,27 @@
     <row r="66" spans="1:30" ht="13">
       <c r="A66" s="29"/>
       <c r="B66" s="30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C66" s="29"/>
       <c r="D66" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="E66" s="29"/>
+      <c r="F66" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="G66" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29" t="s">
+      <c r="H66" s="29" t="s">
         <v>261</v>
-      </c>
-      <c r="H66" s="29" t="s">
-        <v>262</v>
       </c>
       <c r="I66" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J66" s="31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K66" s="32"/>
       <c r="L66" s="33">
@@ -6021,23 +6051,25 @@
     <row r="67" spans="1:30" ht="13">
       <c r="A67" s="29"/>
       <c r="B67" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C67" s="29"/>
       <c r="D67" s="29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
+      <c r="F67" s="29" t="s">
+        <v>264</v>
+      </c>
       <c r="G67" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H67" s="29"/>
       <c r="I67" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J67" s="31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K67" s="35"/>
       <c r="L67" s="33"/>
@@ -6065,23 +6097,25 @@
     <row r="68" spans="1:30" ht="13">
       <c r="A68" s="29"/>
       <c r="B68" s="30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C68" s="29"/>
       <c r="D68" s="29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
+      <c r="F68" s="29" t="s">
+        <v>267</v>
+      </c>
       <c r="G68" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H68" s="29"/>
       <c r="I68" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J68" s="31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K68" s="35">
         <v>43208</v>
@@ -6111,23 +6145,25 @@
     <row r="69" spans="1:30" ht="13">
       <c r="A69" s="29"/>
       <c r="B69" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C69" s="29"/>
       <c r="D69" s="29" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
+      <c r="F69" s="29" t="s">
+        <v>270</v>
+      </c>
       <c r="G69" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H69" s="29"/>
       <c r="I69" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J69" s="31" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K69" s="32"/>
       <c r="L69" s="33">
@@ -6157,23 +6193,25 @@
     <row r="70" spans="1:30" ht="13">
       <c r="A70" s="29"/>
       <c r="B70" s="36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C70" s="29"/>
       <c r="D70" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
+      <c r="F70" s="29" t="s">
+        <v>273</v>
+      </c>
       <c r="G70" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H70" s="29"/>
       <c r="I70" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J70" s="31" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K70" s="32"/>
       <c r="L70" s="33">
@@ -6203,23 +6241,25 @@
     <row r="71" spans="1:30" ht="13">
       <c r="A71" s="29"/>
       <c r="B71" s="36" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C71" s="29"/>
       <c r="D71" s="29" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
+      <c r="F71" s="29" t="s">
+        <v>276</v>
+      </c>
       <c r="G71" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H71" s="29"/>
       <c r="I71" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J71" s="37" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K71" s="32"/>
       <c r="L71" s="33">
@@ -6249,23 +6289,25 @@
     <row r="72" spans="1:30" ht="13">
       <c r="A72" s="29"/>
       <c r="B72" s="30" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C72" s="29"/>
       <c r="D72" s="29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E72" s="29"/>
-      <c r="F72" s="29"/>
+      <c r="F72" s="29" t="s">
+        <v>279</v>
+      </c>
       <c r="G72" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H72" s="29"/>
       <c r="I72" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J72" s="31" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K72" s="32"/>
       <c r="L72" s="33">
@@ -6295,23 +6337,25 @@
     <row r="73" spans="1:30" ht="13">
       <c r="A73" s="29"/>
       <c r="B73" s="30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C73" s="29"/>
       <c r="D73" s="29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E73" s="29"/>
-      <c r="F73" s="29"/>
+      <c r="F73" s="29" t="s">
+        <v>282</v>
+      </c>
       <c r="G73" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H73" s="29"/>
       <c r="I73" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J73" s="31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K73" s="32"/>
       <c r="L73" s="33">
@@ -6341,23 +6385,25 @@
     <row r="74" spans="1:30" ht="13">
       <c r="A74" s="29"/>
       <c r="B74" s="30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C74" s="29"/>
       <c r="D74" s="29" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E74" s="29"/>
-      <c r="F74" s="29"/>
+      <c r="F74" s="29" t="s">
+        <v>285</v>
+      </c>
       <c r="G74" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H74" s="29"/>
       <c r="I74" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J74" s="31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K74" s="32"/>
       <c r="L74" s="33">
@@ -6387,23 +6433,25 @@
     <row r="75" spans="1:30" ht="13">
       <c r="A75" s="29"/>
       <c r="B75" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C75" s="29"/>
       <c r="D75" s="29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E75" s="29"/>
-      <c r="F75" s="29"/>
+      <c r="F75" s="29" t="s">
+        <v>288</v>
+      </c>
       <c r="G75" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H75" s="29"/>
       <c r="I75" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J75" s="31" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K75" s="32"/>
       <c r="L75" s="33">
@@ -6433,23 +6481,25 @@
     <row r="76" spans="1:30" ht="13">
       <c r="A76" s="29"/>
       <c r="B76" s="30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C76" s="29"/>
       <c r="D76" s="29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E76" s="29"/>
-      <c r="F76" s="29"/>
+      <c r="F76" s="29" t="s">
+        <v>291</v>
+      </c>
       <c r="G76" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H76" s="29"/>
       <c r="I76" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J76" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K76" s="32"/>
       <c r="L76" s="33">
@@ -6479,23 +6529,25 @@
     <row r="77" spans="1:30" ht="13">
       <c r="A77" s="29"/>
       <c r="B77" s="30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C77" s="29"/>
       <c r="D77" s="29" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E77" s="29"/>
-      <c r="F77" s="29"/>
+      <c r="F77" s="29" t="s">
+        <v>294</v>
+      </c>
       <c r="G77" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H77" s="29"/>
       <c r="I77" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J77" s="31" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K77" s="32"/>
       <c r="L77" s="33">
@@ -6525,23 +6577,25 @@
     <row r="78" spans="1:30" ht="13">
       <c r="A78" s="29"/>
       <c r="B78" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C78" s="29"/>
       <c r="D78" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E78" s="29"/>
-      <c r="F78" s="29"/>
+      <c r="F78" s="29" t="s">
+        <v>297</v>
+      </c>
       <c r="G78" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H78" s="29"/>
       <c r="I78" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J78" s="37" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K78" s="32"/>
       <c r="L78" s="33">
@@ -6571,23 +6625,25 @@
     <row r="79" spans="1:30" ht="13">
       <c r="A79" s="29"/>
       <c r="B79" s="30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C79" s="29"/>
       <c r="D79" s="29" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E79" s="29"/>
-      <c r="F79" s="29"/>
+      <c r="F79" s="29" t="s">
+        <v>300</v>
+      </c>
       <c r="G79" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H79" s="29"/>
       <c r="I79" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J79" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K79" s="32"/>
       <c r="L79" s="33">
@@ -6617,23 +6673,25 @@
     <row r="80" spans="1:30" ht="13">
       <c r="A80" s="29"/>
       <c r="B80" s="30" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C80" s="29"/>
       <c r="D80" s="29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E80" s="29"/>
-      <c r="F80" s="29"/>
+      <c r="F80" s="29" t="s">
+        <v>303</v>
+      </c>
       <c r="G80" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H80" s="29"/>
       <c r="I80" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J80" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K80" s="32"/>
       <c r="L80" s="33">
@@ -6663,23 +6721,25 @@
     <row r="81" spans="1:30" ht="13">
       <c r="A81" s="29"/>
       <c r="B81" s="30" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C81" s="29"/>
       <c r="D81" s="29" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E81" s="29"/>
-      <c r="F81" s="29"/>
+      <c r="F81" s="29" t="s">
+        <v>306</v>
+      </c>
       <c r="G81" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H81" s="29"/>
       <c r="I81" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J81" s="31" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K81" s="32"/>
       <c r="L81" s="33">
@@ -6709,23 +6769,25 @@
     <row r="82" spans="1:30" ht="13">
       <c r="A82" s="29"/>
       <c r="B82" s="30" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C82" s="29"/>
       <c r="D82" s="29" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E82" s="29"/>
-      <c r="F82" s="29"/>
+      <c r="F82" s="29" t="s">
+        <v>309</v>
+      </c>
       <c r="G82" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H82" s="29"/>
       <c r="I82" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J82" s="37" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K82" s="32"/>
       <c r="L82" s="33">
@@ -6755,23 +6817,25 @@
     <row r="83" spans="1:30" ht="13">
       <c r="A83" s="29"/>
       <c r="B83" s="30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C83" s="29"/>
       <c r="D83" s="29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E83" s="29"/>
-      <c r="F83" s="29"/>
+      <c r="F83" s="29" t="s">
+        <v>312</v>
+      </c>
       <c r="G83" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H83" s="29"/>
       <c r="I83" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J83" s="31" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K83" s="32"/>
       <c r="L83" s="33">
@@ -6801,23 +6865,25 @@
     <row r="84" spans="1:30" ht="13">
       <c r="A84" s="29"/>
       <c r="B84" s="30" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C84" s="29"/>
       <c r="D84" s="29" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E84" s="29"/>
-      <c r="F84" s="29"/>
+      <c r="F84" s="29" t="s">
+        <v>315</v>
+      </c>
       <c r="G84" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H84" s="29"/>
       <c r="I84" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J84" s="31" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K84" s="32"/>
       <c r="L84" s="33">
@@ -6847,23 +6913,25 @@
     <row r="85" spans="1:30" ht="13">
       <c r="A85" s="29"/>
       <c r="B85" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C85" s="29"/>
       <c r="D85" s="29" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E85" s="29"/>
-      <c r="F85" s="29"/>
+      <c r="F85" s="29" t="s">
+        <v>318</v>
+      </c>
       <c r="G85" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H85" s="29"/>
       <c r="I85" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J85" s="31" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K85" s="32"/>
       <c r="L85" s="33">
@@ -6893,23 +6961,25 @@
     <row r="86" spans="1:30" ht="13">
       <c r="A86" s="29"/>
       <c r="B86" s="30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C86" s="29"/>
       <c r="D86" s="29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E86" s="29"/>
-      <c r="F86" s="29"/>
+      <c r="F86" s="29" t="s">
+        <v>321</v>
+      </c>
       <c r="G86" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H86" s="29"/>
       <c r="I86" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J86" s="31" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K86" s="35">
         <v>42966</v>
@@ -6941,23 +7011,25 @@
     <row r="87" spans="1:30" ht="13">
       <c r="A87" s="29"/>
       <c r="B87" s="30" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C87" s="29"/>
       <c r="D87" s="29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E87" s="29"/>
-      <c r="F87" s="29"/>
+      <c r="F87" s="29" t="s">
+        <v>324</v>
+      </c>
       <c r="G87" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H87" s="29"/>
       <c r="I87" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J87" s="31" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K87" s="35">
         <v>42966</v>
@@ -6989,23 +7061,25 @@
     <row r="88" spans="1:30" ht="13">
       <c r="A88" s="29"/>
       <c r="B88" s="30" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C88" s="29"/>
       <c r="D88" s="29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E88" s="29"/>
-      <c r="F88" s="29"/>
+      <c r="F88" s="29" t="s">
+        <v>327</v>
+      </c>
       <c r="G88" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H88" s="29"/>
       <c r="I88" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J88" s="31" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K88" s="35">
         <v>42966</v>
@@ -7037,23 +7111,25 @@
     <row r="89" spans="1:30" ht="13">
       <c r="A89" s="29"/>
       <c r="B89" s="30" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C89" s="29"/>
       <c r="D89" s="29" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E89" s="29"/>
-      <c r="F89" s="29"/>
+      <c r="F89" s="29" t="s">
+        <v>330</v>
+      </c>
       <c r="G89" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H89" s="29"/>
       <c r="I89" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J89" s="31" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K89" s="35"/>
       <c r="L89" s="33"/>
@@ -7081,23 +7157,25 @@
     <row r="90" spans="1:30" ht="13">
       <c r="A90" s="29"/>
       <c r="B90" s="30" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C90" s="29"/>
       <c r="D90" s="29" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E90" s="29"/>
-      <c r="F90" s="29"/>
+      <c r="F90" s="29" t="s">
+        <v>333</v>
+      </c>
       <c r="G90" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H90" s="29"/>
       <c r="I90" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J90" s="31" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K90" s="35"/>
       <c r="L90" s="33"/>
@@ -7125,23 +7203,25 @@
     <row r="91" spans="1:30" ht="13">
       <c r="A91" s="29"/>
       <c r="B91" s="30" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C91" s="29"/>
       <c r="D91" s="29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E91" s="29"/>
-      <c r="F91" s="29"/>
+      <c r="F91" s="29" t="s">
+        <v>336</v>
+      </c>
       <c r="G91" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H91" s="29"/>
       <c r="I91" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J91" s="31" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K91" s="35"/>
       <c r="L91" s="33"/>
@@ -7169,23 +7249,25 @@
     <row r="92" spans="1:30" ht="13">
       <c r="A92" s="29"/>
       <c r="B92" s="30" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C92" s="29"/>
       <c r="D92" s="29" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E92" s="29"/>
-      <c r="F92" s="29"/>
+      <c r="F92" s="29" t="s">
+        <v>338</v>
+      </c>
       <c r="G92" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H92" s="29"/>
       <c r="I92" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J92" s="31" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K92" s="35"/>
       <c r="L92" s="33"/>
@@ -7213,23 +7295,25 @@
     <row r="93" spans="1:30" ht="13">
       <c r="A93" s="29"/>
       <c r="B93" s="30" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C93" s="29"/>
       <c r="D93" s="29" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E93" s="29"/>
-      <c r="F93" s="29"/>
+      <c r="F93" s="29" t="s">
+        <v>341</v>
+      </c>
       <c r="G93" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H93" s="29"/>
       <c r="I93" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J93" s="31" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K93" s="35"/>
       <c r="L93" s="33"/>
@@ -7257,23 +7341,25 @@
     <row r="94" spans="1:30" ht="13">
       <c r="A94" s="29"/>
       <c r="B94" s="30" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C94" s="29"/>
       <c r="D94" s="29" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E94" s="29"/>
-      <c r="F94" s="29"/>
+      <c r="F94" s="29" t="s">
+        <v>344</v>
+      </c>
       <c r="G94" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H94" s="29"/>
       <c r="I94" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J94" s="31" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K94" s="35">
         <v>43174</v>
@@ -7305,23 +7391,25 @@
     <row r="95" spans="1:30" ht="13">
       <c r="A95" s="29"/>
       <c r="B95" s="30" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C95" s="29"/>
       <c r="D95" s="29" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E95" s="29"/>
-      <c r="F95" s="29"/>
+      <c r="F95" s="29" t="s">
+        <v>347</v>
+      </c>
       <c r="G95" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H95" s="29"/>
       <c r="I95" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J95" s="31" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K95" s="35"/>
       <c r="L95" s="33"/>
@@ -7349,23 +7437,25 @@
     <row r="96" spans="1:30" ht="13">
       <c r="A96" s="29"/>
       <c r="B96" s="30" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C96" s="29"/>
       <c r="D96" s="29" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E96" s="29"/>
-      <c r="F96" s="29"/>
+      <c r="F96" s="29" t="s">
+        <v>350</v>
+      </c>
       <c r="G96" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H96" s="29"/>
       <c r="I96" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J96" s="31" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K96" s="35"/>
       <c r="L96" s="33"/>
@@ -7393,23 +7483,25 @@
     <row r="97" spans="1:30" ht="13">
       <c r="A97" s="29"/>
       <c r="B97" s="30" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C97" s="29"/>
       <c r="D97" s="29" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E97" s="29"/>
-      <c r="F97" s="29"/>
+      <c r="F97" s="29" t="s">
+        <v>353</v>
+      </c>
       <c r="G97" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H97" s="29"/>
       <c r="I97" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J97" s="31" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K97" s="35">
         <v>43208</v>
@@ -7439,23 +7531,25 @@
     <row r="98" spans="1:30" ht="13">
       <c r="A98" s="29"/>
       <c r="B98" s="30" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C98" s="29"/>
       <c r="D98" s="29" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E98" s="29"/>
-      <c r="F98" s="29"/>
+      <c r="F98" s="29" t="s">
+        <v>356</v>
+      </c>
       <c r="G98" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H98" s="29"/>
       <c r="I98" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J98" s="31" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K98" s="35">
         <v>43208</v>
@@ -7485,23 +7579,25 @@
     <row r="99" spans="1:30" ht="13">
       <c r="A99" s="29"/>
       <c r="B99" s="30" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C99" s="29"/>
       <c r="D99" s="29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E99" s="29"/>
-      <c r="F99" s="29"/>
+      <c r="F99" s="29" t="s">
+        <v>359</v>
+      </c>
       <c r="G99" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H99" s="29"/>
       <c r="I99" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J99" s="31" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K99" s="35">
         <v>43208</v>
@@ -7512,7 +7608,7 @@
       </c>
       <c r="N99" s="32"/>
       <c r="O99" s="38" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P99" s="32"/>
       <c r="Q99" s="32"/>
@@ -7533,23 +7629,25 @@
     <row r="100" spans="1:30" ht="13">
       <c r="A100" s="29"/>
       <c r="B100" s="30" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C100" s="29"/>
       <c r="D100" s="29" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E100" s="29"/>
-      <c r="F100" s="29"/>
+      <c r="F100" s="29" t="s">
+        <v>362</v>
+      </c>
       <c r="G100" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H100" s="29"/>
       <c r="I100" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J100" s="31" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K100" s="35">
         <v>43208</v>
@@ -7579,25 +7677,27 @@
     <row r="101" spans="1:30" ht="13">
       <c r="A101" s="39"/>
       <c r="B101" s="40" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C101" s="39"/>
       <c r="D101" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="E101" s="39"/>
+      <c r="F101" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="G101" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="E101" s="39"/>
-      <c r="F101" s="39"/>
-      <c r="G101" s="39" t="s">
+      <c r="H101" s="39" t="s">
         <v>367</v>
-      </c>
-      <c r="H101" s="39" t="s">
-        <v>368</v>
       </c>
       <c r="I101" s="39" t="s">
         <v>20</v>
       </c>
       <c r="J101" s="41" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K101" s="42"/>
       <c r="L101" s="42"/>
@@ -7625,29 +7725,31 @@
     <row r="102" spans="1:30" ht="13">
       <c r="A102" s="39"/>
       <c r="B102" s="40" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C102" s="39"/>
       <c r="D102" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="E102" s="39"/>
+      <c r="F102" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="G102" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="H102" s="39" t="s">
         <v>371</v>
-      </c>
-      <c r="E102" s="39"/>
-      <c r="F102" s="39"/>
-      <c r="G102" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="H102" s="39" t="s">
-        <v>372</v>
       </c>
       <c r="I102" s="39" t="s">
         <v>20</v>
       </c>
       <c r="J102" s="41" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K102" s="42"/>
       <c r="L102" s="42" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M102" s="43">
         <v>43867</v>
@@ -11415,34 +11517,34 @@
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" customHeight="1">
       <c r="A1" s="44" t="s">
+        <v>374</v>
+      </c>
+      <c r="B1" s="44" t="s">
         <v>375</v>
-      </c>
-      <c r="B1" s="44" t="s">
-        <v>376</v>
       </c>
       <c r="C1" s="44" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="44" t="s">
+        <v>376</v>
+      </c>
+      <c r="E1" s="45" t="s">
         <v>377</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="F1" s="45" t="s">
         <v>378</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="G1" s="46" t="s">
         <v>379</v>
       </c>
-      <c r="G1" s="46" t="s">
+      <c r="H1" s="47" t="s">
         <v>380</v>
       </c>
-      <c r="H1" s="47" t="s">
+      <c r="I1" s="46" t="s">
         <v>381</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="J1" s="45" t="s">
         <v>382</v>
-      </c>
-      <c r="J1" s="45" t="s">
-        <v>383</v>
       </c>
       <c r="L1" s="48"/>
       <c r="M1" s="48"/>
@@ -11454,23 +11556,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C2" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D2" s="50" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2" s="51" t="s">
         <v>385</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>386</v>
       </c>
       <c r="F2" s="51"/>
       <c r="G2" s="52">
         <v>46083</v>
       </c>
       <c r="H2" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I2" s="52"/>
       <c r="J2" s="51"/>
@@ -11484,23 +11586,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="50" t="s">
+        <v>387</v>
+      </c>
+      <c r="C3" s="50" t="s">
         <v>388</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="D3" s="50" t="s">
         <v>389</v>
       </c>
-      <c r="D3" s="50" t="s">
-        <v>390</v>
-      </c>
       <c r="E3" s="51" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F3" s="51"/>
       <c r="G3" s="52">
         <v>46083</v>
       </c>
       <c r="H3" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I3" s="52">
         <v>45845</v>
@@ -11516,23 +11618,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C4" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E4" s="51" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F4" s="51"/>
       <c r="G4" s="52">
         <v>46083</v>
       </c>
       <c r="H4" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I4" s="52"/>
       <c r="J4" s="51"/>
@@ -11546,13 +11648,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="50" t="s">
+        <v>387</v>
+      </c>
+      <c r="C5" s="50" t="s">
         <v>388</v>
       </c>
-      <c r="C5" s="50" t="s">
-        <v>389</v>
-      </c>
       <c r="D5" s="50" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E5" s="51"/>
       <c r="F5" s="51"/>
@@ -11560,7 +11662,7 @@
         <v>46083</v>
       </c>
       <c r="H5" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I5" s="52"/>
       <c r="J5" s="51"/>
@@ -11574,13 +11676,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
@@ -11598,23 +11700,23 @@
         <v>6</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="50" t="s">
+        <v>403</v>
+      </c>
+      <c r="E7" s="51" t="s">
         <v>404</v>
-      </c>
-      <c r="E7" s="51" t="s">
-        <v>405</v>
       </c>
       <c r="F7" s="51"/>
       <c r="G7" s="52">
         <v>46084</v>
       </c>
       <c r="H7" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I7" s="52"/>
       <c r="J7" s="51"/>
@@ -11628,23 +11730,23 @@
         <v>7</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="50" t="s">
+        <v>392</v>
+      </c>
+      <c r="E8" s="51" t="s">
         <v>393</v>
-      </c>
-      <c r="E8" s="51" t="s">
-        <v>394</v>
       </c>
       <c r="F8" s="51"/>
       <c r="G8" s="52">
         <v>46083</v>
       </c>
       <c r="H8" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I8" s="52"/>
       <c r="J8" s="51"/>
@@ -11658,10 +11760,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D9" s="50"/>
       <c r="E9" s="51"/>
@@ -11670,7 +11772,7 @@
         <v>46083</v>
       </c>
       <c r="H9" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I9" s="52"/>
       <c r="J9" s="51"/>
@@ -11684,14 +11786,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="50" t="s">
+        <v>415</v>
+      </c>
+      <c r="C10" s="50" t="s">
         <v>416</v>
-      </c>
-      <c r="C10" s="50" t="s">
-        <v>417</v>
       </c>
       <c r="D10" s="50"/>
       <c r="E10" s="51" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F10" s="51"/>
       <c r="G10" s="52"/>
@@ -11708,7 +11810,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C11" s="50" t="s">
         <v>44</v>
@@ -11720,7 +11822,7 @@
         <v>46083</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I11" s="52"/>
       <c r="J11" s="51"/>
@@ -11734,16 +11836,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="50" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" s="50" t="s">
         <v>419</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="D12" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="D12" s="50" t="s">
-        <v>421</v>
-      </c>
       <c r="E12" s="51" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F12" s="51"/>
       <c r="G12" s="52"/>
@@ -11760,21 +11862,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D13" s="50"/>
       <c r="E13" s="51" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F13" s="51"/>
       <c r="G13" s="52"/>
       <c r="H13" s="52"/>
       <c r="I13" s="52"/>
       <c r="J13" s="51" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L13" s="48"/>
       <c r="M13" s="48"/>
@@ -11786,14 +11888,14 @@
         <v>13</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D14" s="50"/>
       <c r="E14" s="51" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F14" s="51"/>
       <c r="G14" s="52"/>
@@ -11810,13 +11912,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="50" t="s">
+        <v>405</v>
+      </c>
+      <c r="C15" s="50" t="s">
         <v>406</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="D15" s="50" t="s">
         <v>407</v>
-      </c>
-      <c r="D15" s="50" t="s">
-        <v>408</v>
       </c>
       <c r="E15" s="51"/>
       <c r="F15" s="51"/>
@@ -11824,7 +11926,7 @@
         <v>46084</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I15" s="52">
         <v>45845</v>
@@ -11840,13 +11942,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C16" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E16" s="51"/>
       <c r="F16" s="51"/>
@@ -11854,7 +11956,7 @@
         <v>46084</v>
       </c>
       <c r="H16" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I16" s="52">
         <v>45845</v>
@@ -11870,13 +11972,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C17" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E17" s="51"/>
       <c r="F17" s="51"/>
@@ -11884,7 +11986,7 @@
         <v>46083</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I17" s="52"/>
       <c r="J17" s="51"/>
@@ -11898,21 +12000,21 @@
         <v>26</v>
       </c>
       <c r="B18" s="50" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E18" s="51"/>
       <c r="F18" s="51"/>
-      <c r="G18" s="99">
+      <c r="G18" s="98">
         <v>46083</v>
       </c>
-      <c r="H18" s="101" t="s">
-        <v>387</v>
+      <c r="H18" s="99" t="s">
+        <v>386</v>
       </c>
       <c r="I18" s="52"/>
       <c r="J18" s="51"/>
@@ -11926,13 +12028,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C19" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E19" s="51"/>
       <c r="F19" s="51"/>
@@ -11940,7 +12042,7 @@
         <v>46084</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I19" s="52"/>
       <c r="J19" s="51"/>
@@ -11954,21 +12056,21 @@
         <v>18</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C20" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="50" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E20" s="51"/>
       <c r="F20" s="51"/>
-      <c r="G20" s="98">
+      <c r="G20" s="52">
         <v>46084</v>
       </c>
-      <c r="H20" s="100" t="s">
-        <v>387</v>
+      <c r="H20" s="51" t="s">
+        <v>386</v>
       </c>
       <c r="I20" s="52"/>
       <c r="J20" s="51"/>
@@ -11982,13 +12084,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E21" s="51"/>
       <c r="F21" s="51"/>
@@ -12006,7 +12108,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C22" s="50" t="s">
         <v>44</v>
@@ -12018,7 +12120,7 @@
         <v>46083</v>
       </c>
       <c r="H22" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I22" s="52"/>
       <c r="J22" s="51"/>
@@ -12032,13 +12134,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C23" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D23" s="50" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E23" s="51"/>
       <c r="F23" s="51"/>
@@ -12046,7 +12148,7 @@
         <v>46084</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I23" s="52"/>
       <c r="J23" s="51"/>
@@ -12060,13 +12162,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C24" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E24" s="51"/>
       <c r="F24" s="51"/>
@@ -12074,7 +12176,7 @@
         <v>46084</v>
       </c>
       <c r="H24" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I24" s="52"/>
       <c r="J24" s="51"/>
@@ -12088,13 +12190,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="50" t="s">
+        <v>412</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="D25" s="50" t="s">
         <v>413</v>
-      </c>
-      <c r="C25" s="50" t="s">
-        <v>420</v>
-      </c>
-      <c r="D25" s="50" t="s">
-        <v>414</v>
       </c>
       <c r="E25" s="51"/>
       <c r="F25" s="51"/>
@@ -12112,13 +12214,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C26" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D26" s="50" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E26" s="51"/>
       <c r="F26" s="51"/>
@@ -12126,7 +12228,7 @@
         <v>46083</v>
       </c>
       <c r="H26" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I26" s="52"/>
       <c r="J26" s="51"/>
@@ -12140,13 +12242,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C27" s="50" t="s">
         <v>44</v>
       </c>
       <c r="D27" s="50" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E27" s="51"/>
       <c r="F27" s="51"/>
@@ -12154,7 +12256,7 @@
         <v>46083</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I27" s="52"/>
       <c r="J27" s="51"/>
@@ -17060,10 +17162,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1">
       <c r="A1" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>424</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1">
@@ -17071,7 +17173,7 @@
         <v>43</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1">
@@ -17079,7 +17181,7 @@
         <v>178</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1">
@@ -17087,7 +17189,7 @@
         <v>107</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1">
@@ -17095,7 +17197,7 @@
         <v>111</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1">
@@ -17103,7 +17205,7 @@
         <v>183</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1">
@@ -17111,7 +17213,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1">
@@ -17119,7 +17221,7 @@
         <v>17</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1">
@@ -17127,7 +17229,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" customHeight="1">
@@ -17135,7 +17237,7 @@
         <v>119</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1">
@@ -17143,7 +17245,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1">
@@ -17151,7 +17253,7 @@
         <v>188</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" customHeight="1">
@@ -17159,7 +17261,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" customHeight="1">
@@ -17167,15 +17269,15 @@
         <v>193</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75" customHeight="1">
@@ -17183,7 +17285,7 @@
         <v>198</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1">
@@ -17196,7 +17298,7 @@
         <v>126</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1">
@@ -17204,7 +17306,7 @@
         <v>53</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.75" customHeight="1">
@@ -17212,15 +17314,15 @@
         <v>34</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1">
@@ -17233,7 +17335,7 @@
         <v>201</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1">
@@ -17241,7 +17343,7 @@
         <v>203</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" customHeight="1">
@@ -17249,7 +17351,7 @@
         <v>205</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1">
@@ -17262,12 +17364,12 @@
         <v>57</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15.75" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15.75" customHeight="1">
@@ -17277,10 +17379,10 @@
     </row>
     <row r="30" spans="1:2" ht="15.75" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15.75" customHeight="1">
@@ -17288,7 +17390,7 @@
         <v>207</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15.75" customHeight="1">
@@ -17296,7 +17398,7 @@
         <v>38</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.75" customHeight="1">
@@ -17306,10 +17408,10 @@
     </row>
     <row r="34" spans="1:2" ht="15.75" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" customHeight="1">
@@ -17317,7 +17419,7 @@
         <v>65</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.75" customHeight="1">
@@ -17325,17 +17427,17 @@
         <v>86</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.75" customHeight="1">
       <c r="A37" s="13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.75" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.75" customHeight="1">
@@ -17343,12 +17445,12 @@
         <v>90</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15.75" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.75" customHeight="1">
@@ -17356,7 +17458,7 @@
         <v>69</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15.75" customHeight="1">
@@ -17364,7 +17466,7 @@
         <v>73</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15.75" customHeight="1">
@@ -17372,12 +17474,12 @@
         <v>78</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.75" customHeight="1">
       <c r="A44" s="13" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15.75" customHeight="1">
@@ -17385,7 +17487,7 @@
         <v>82</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15.75" customHeight="1">
@@ -17393,22 +17495,22 @@
         <v>94</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15.75" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="15.75" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" customHeight="1">
@@ -17416,7 +17518,7 @@
         <v>98</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" customHeight="1">
@@ -17424,17 +17526,17 @@
         <v>102</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15.75" customHeight="1">
       <c r="A52" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" customHeight="1">
       <c r="A53" s="13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" customHeight="1">
@@ -17442,20 +17544,20 @@
         <v>231</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15.75" customHeight="1">
       <c r="A55" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" customHeight="1">
       <c r="A56" s="13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15.75" customHeight="1">
@@ -17463,7 +17565,7 @@
         <v>132</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15.75" customHeight="1">
@@ -17471,22 +17573,22 @@
         <v>139</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" customHeight="1">
       <c r="A59" s="13" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" customHeight="1">
       <c r="A60" s="13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" customHeight="1">
       <c r="A61" s="13" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="15.75" customHeight="1">
@@ -17494,22 +17596,22 @@
         <v>155</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15.75" customHeight="1">
       <c r="A63" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" customHeight="1">
       <c r="A64" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="15.75" customHeight="1">
       <c r="A65" s="13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="15.75" customHeight="1">
@@ -17517,12 +17619,12 @@
         <v>142</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="15.75" customHeight="1">
       <c r="A67" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="15.75" customHeight="1">
@@ -17530,7 +17632,7 @@
         <v>164</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="15.75" customHeight="1">
@@ -17538,12 +17640,12 @@
         <v>235</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="15.75" customHeight="1">
       <c r="A70" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="15.75" customHeight="1">
@@ -17551,12 +17653,12 @@
         <v>239</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="15.75" customHeight="1">
       <c r="A72" s="13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="15.75" customHeight="1">
@@ -17564,7 +17666,7 @@
         <v>221</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="15.75" customHeight="1">
@@ -17572,17 +17674,17 @@
         <v>167</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="15.75" customHeight="1">
       <c r="A75" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="15.75" customHeight="1">
       <c r="A76" s="13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="15.75" customHeight="1">
@@ -17590,12 +17692,12 @@
         <v>224</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="15.75" customHeight="1">
       <c r="A78" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="15.75" customHeight="1">
@@ -17603,12 +17705,12 @@
         <v>227</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="15.75" customHeight="1">
       <c r="A80" s="13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="15.75" customHeight="1">
@@ -17616,7 +17718,7 @@
         <v>158</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="15.75" customHeight="1">
@@ -17624,17 +17726,17 @@
         <v>145</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="15.75" customHeight="1">
       <c r="A83" s="13" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="15.75" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="15.75" customHeight="1">
@@ -17642,12 +17744,12 @@
         <v>161</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="15.75" customHeight="1">
       <c r="A86" s="13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="15.75" customHeight="1">
@@ -17655,7 +17757,7 @@
         <v>148</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="13">
@@ -17663,20 +17765,20 @@
         <v>151</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="13">
       <c r="A89" s="13" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="13">
       <c r="A90" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="13">
@@ -17684,7 +17786,7 @@
         <v>169</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="13">
@@ -17692,7 +17794,7 @@
         <v>174</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="13">
@@ -17702,12 +17804,12 @@
     </row>
     <row r="94" spans="1:2" ht="13">
       <c r="A94" s="13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="13">
       <c r="A95" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -19327,7 +19429,7 @@
         <v>66</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G1" s="57"/>
     </row>
@@ -19345,13 +19447,13 @@
         <v>99</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G2" s="57"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>18</v>
@@ -19360,18 +19462,18 @@
         <v>4799743022</v>
       </c>
       <c r="D3" s="56" t="s">
+        <v>464</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="G3" s="57" t="s">
         <v>465</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="G3" s="57" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>18</v>
@@ -19380,16 +19482,16 @@
         <v>11330090030</v>
       </c>
       <c r="D4" s="56" t="s">
+        <v>467</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>468</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>469</v>
       </c>
       <c r="G4" s="57"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>18</v>
@@ -19398,10 +19500,10 @@
         <v>13506872366</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G5" s="57"/>
     </row>
@@ -19419,7 +19521,7 @@
         <v>91</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F6" s="58">
         <v>42947</v>
@@ -19440,7 +19542,7 @@
         <v>70</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F7" s="58">
         <v>42947</v>
@@ -19449,7 +19551,7 @@
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>18</v>
@@ -19458,21 +19560,21 @@
         <v>15842099774</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F8" s="58">
         <v>42947</v>
       </c>
       <c r="G8" s="57" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="13" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>18</v>
@@ -19481,10 +19583,10 @@
         <v>24246898238</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F9" s="58">
         <v>42947</v>
@@ -19505,7 +19607,7 @@
         <v>21</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F10" s="58">
         <v>42947</v>
@@ -19516,7 +19618,7 @@
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>18</v>
@@ -19525,10 +19627,10 @@
         <v>2541268622</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F11" s="58">
         <v>42947</v>
@@ -19537,7 +19639,7 @@
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>18</v>
@@ -19546,21 +19648,21 @@
         <v>15539768894</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F12" s="58">
         <v>42947</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>18</v>
@@ -19569,10 +19671,10 @@
         <v>41782089278</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F13" s="58">
         <v>42947</v>
@@ -19581,7 +19683,7 @@
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="13" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>18</v>
@@ -19590,10 +19692,10 @@
         <v>35191276094</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F14" s="58">
         <v>42948</v>
@@ -19614,7 +19716,7 @@
         <v>87</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F15" s="58">
         <v>43296</v>
@@ -19635,7 +19737,7 @@
         <v>83</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F16" s="58">
         <v>43296</v>
@@ -19656,7 +19758,7 @@
         <v>79</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F17" s="58">
         <v>43296</v>
@@ -19665,7 +19767,7 @@
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>18</v>
@@ -19674,10 +19776,10 @@
         <v>15378607694</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F18" s="58">
         <v>43320</v>
@@ -19686,7 +19788,7 @@
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>18</v>
@@ -19695,16 +19797,16 @@
         <v>19732172366</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F19" s="58">
         <v>43320</v>
       </c>
       <c r="G19" s="57" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
@@ -19721,7 +19823,7 @@
         <v>112</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F20" s="58">
         <v>43320</v>
@@ -19742,7 +19844,7 @@
         <v>75</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F21" s="58">
         <v>43320</v>
@@ -19763,7 +19865,7 @@
         <v>124</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F22" s="58">
         <v>43320</v>
@@ -19772,7 +19874,7 @@
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>18</v>
@@ -19781,21 +19883,21 @@
         <v>13201825358</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F23" s="58">
         <v>43320</v>
       </c>
       <c r="G23" s="57" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>18</v>
@@ -19804,21 +19906,21 @@
         <v>28439301710</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F24" s="58">
         <v>43320</v>
       </c>
       <c r="G24" s="57" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>18</v>
@@ -19827,10 +19929,10 @@
         <v>11025043022</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F25" s="58">
         <v>43320</v>
@@ -22810,22 +22912,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
       <c r="A2" s="59" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1">
       <c r="A4" s="60" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
       <c r="A6" s="60" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
@@ -22844,7 +22946,7 @@
         <v>130</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
@@ -22863,10 +22965,10 @@
         <v>3</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
@@ -22874,10 +22976,10 @@
         <v>4</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1">
@@ -22918,13 +23020,13 @@
         <v>8</v>
       </c>
       <c r="D16" s="62" t="s">
+        <v>505</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>506</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="F16" s="13" t="s">
         <v>507</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>508</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" ref="G16:G28" si="0">CONCATENATE(D16,E16,F16)</f>
@@ -22936,13 +23038,13 @@
         <v>9</v>
       </c>
       <c r="D17" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" si="0"/>
@@ -22954,13 +23056,13 @@
         <v>10</v>
       </c>
       <c r="D18" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" si="0"/>
@@ -22972,13 +23074,13 @@
         <v>11</v>
       </c>
       <c r="D19" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="0"/>
@@ -22990,13 +23092,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" si="0"/>
@@ -23008,13 +23110,13 @@
         <v>13</v>
       </c>
       <c r="D21" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" si="0"/>
@@ -23026,13 +23128,13 @@
         <v>14</v>
       </c>
       <c r="D22" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" si="0"/>
@@ -23044,13 +23146,13 @@
         <v>15</v>
       </c>
       <c r="D23" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" si="0"/>
@@ -23062,13 +23164,13 @@
         <v>16</v>
       </c>
       <c r="D24" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" si="0"/>
@@ -23080,13 +23182,13 @@
         <v>17</v>
       </c>
       <c r="D25" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="0"/>
@@ -23098,13 +23200,13 @@
         <v>18</v>
       </c>
       <c r="D26" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G26" t="str">
         <f t="shared" si="0"/>
@@ -23116,13 +23218,13 @@
         <v>19</v>
       </c>
       <c r="D27" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G27" t="str">
         <f t="shared" si="0"/>
@@ -23134,13 +23236,13 @@
         <v>20</v>
       </c>
       <c r="D28" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G28" t="str">
         <f t="shared" si="0"/>
@@ -23282,7 +23384,7 @@
         <v>133</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
@@ -23542,7 +23644,7 @@
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>133</v>
@@ -23732,13 +23834,13 @@
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>133</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
@@ -23808,13 +23910,13 @@
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>133</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
@@ -23982,24 +24084,24 @@
     </row>
     <row r="2" spans="1:30" ht="13">
       <c r="A2" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C2" s="64"/>
       <c r="D2" s="64" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E2" s="64"/>
       <c r="F2" s="64"/>
       <c r="G2" s="64" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H2" s="64"/>
       <c r="I2" s="64"/>
       <c r="J2" s="66" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K2" s="64"/>
       <c r="L2" s="64"/>
@@ -24024,14 +24126,14 @@
     </row>
     <row r="3" spans="1:30" ht="13">
       <c r="A3" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B3" s="6">
         <v>17297061950</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -24042,10 +24144,10 @@
         <v>19</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="67">
@@ -24074,14 +24176,14 @@
     </row>
     <row r="4" spans="1:30" ht="13">
       <c r="A4" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B4" s="6">
         <v>2662200974</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -24092,10 +24194,10 @@
         <v>19</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K4" s="8">
         <v>42947</v>
@@ -24126,14 +24228,14 @@
     </row>
     <row r="5" spans="1:30" ht="13">
       <c r="A5" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B5" s="6">
         <v>6953571902</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -24144,10 +24246,10 @@
         <v>19</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K5" s="8">
         <v>42947</v>
@@ -24178,14 +24280,14 @@
     </row>
     <row r="6" spans="1:30" ht="13">
       <c r="A6" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B6" s="6">
         <v>39004419134</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -24196,10 +24298,10 @@
         <v>19</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="67">
@@ -24228,14 +24330,14 @@
     </row>
     <row r="7" spans="1:30" ht="13">
       <c r="A7" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B7" s="6">
         <v>4799743022</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -24246,10 +24348,10 @@
         <v>19</v>
       </c>
       <c r="I7" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="67">
@@ -24260,7 +24362,7 @@
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
@@ -24280,14 +24382,14 @@
     </row>
     <row r="8" spans="1:30" ht="13">
       <c r="A8" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B8" s="6">
         <v>11330090030</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -24298,10 +24400,10 @@
         <v>19</v>
       </c>
       <c r="I8" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="67">
@@ -24330,14 +24432,14 @@
     </row>
     <row r="9" spans="1:30" ht="13">
       <c r="A9" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B9" s="6">
         <v>13201825358</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -24348,10 +24450,10 @@
         <v>74</v>
       </c>
       <c r="I9" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K9" s="8">
         <v>43320</v>
@@ -24364,7 +24466,7 @@
       </c>
       <c r="N9" s="10"/>
       <c r="O9" s="10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="P9" s="10"/>
       <c r="Q9" s="10"/>
@@ -24384,14 +24486,14 @@
     </row>
     <row r="10" spans="1:30" ht="13">
       <c r="A10" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B10" s="6">
         <v>13506872366</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -24402,10 +24504,10 @@
         <v>19</v>
       </c>
       <c r="I10" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="67">
@@ -24434,14 +24536,14 @@
     </row>
     <row r="11" spans="1:30" ht="13">
       <c r="A11" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B11" s="6">
         <v>15378607694</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -24452,10 +24554,10 @@
         <v>74</v>
       </c>
       <c r="I11" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K11" s="8">
         <v>43320</v>
@@ -24486,14 +24588,14 @@
     </row>
     <row r="12" spans="1:30" ht="13">
       <c r="A12" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B12" s="6">
         <v>15539768894</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -24504,10 +24606,10 @@
         <v>19</v>
       </c>
       <c r="I12" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K12" s="8">
         <v>42947</v>
@@ -24520,7 +24622,7 @@
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
@@ -24540,14 +24642,14 @@
     </row>
     <row r="13" spans="1:30" ht="13">
       <c r="A13" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B13" s="6">
         <v>15842099774</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -24558,10 +24660,10 @@
         <v>19</v>
       </c>
       <c r="I13" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K13" s="8">
         <v>42947</v>
@@ -24574,7 +24676,7 @@
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
@@ -24594,14 +24696,14 @@
     </row>
     <row r="14" spans="1:30" ht="13">
       <c r="A14" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B14" s="6">
         <v>19732172366</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -24612,10 +24714,10 @@
         <v>74</v>
       </c>
       <c r="I14" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="K14" s="8">
         <v>43320</v>
@@ -24628,7 +24730,7 @@
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
@@ -24648,14 +24750,14 @@
     </row>
     <row r="15" spans="1:30" ht="13">
       <c r="A15" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B15" s="6">
         <v>24246898238</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -24666,10 +24768,10 @@
         <v>19</v>
       </c>
       <c r="I15" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K15" s="8">
         <v>42947</v>
@@ -24700,14 +24802,14 @@
     </row>
     <row r="16" spans="1:30" ht="13">
       <c r="A16" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B16" s="6">
         <v>28439301710</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -24718,10 +24820,10 @@
         <v>74</v>
       </c>
       <c r="I16" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K16" s="8">
         <v>43320</v>
@@ -24734,7 +24836,7 @@
       </c>
       <c r="N16" s="10"/>
       <c r="O16" s="10" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
@@ -24754,14 +24856,14 @@
     </row>
     <row r="17" spans="1:30" ht="13">
       <c r="A17" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B17" s="6">
         <v>17555390030</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -24775,7 +24877,7 @@
         <v>20</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K17" s="8">
         <v>43320</v>
@@ -24788,7 +24890,7 @@
       </c>
       <c r="N17" s="10"/>
       <c r="O17" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
@@ -24808,14 +24910,14 @@
     </row>
     <row r="18" spans="1:30" ht="13">
       <c r="A18" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B18" s="6">
         <v>32792866382</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -24829,7 +24931,7 @@
         <v>20</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K18" s="8">
         <v>43320</v>
@@ -24842,7 +24944,7 @@
       </c>
       <c r="N18" s="10"/>
       <c r="O18" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="P18" s="10"/>
       <c r="Q18" s="10"/>
@@ -24862,14 +24964,14 @@
     </row>
     <row r="19" spans="1:30" ht="13">
       <c r="A19" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B19" s="6">
         <v>4716323390</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -24883,7 +24985,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K19" s="8">
         <v>42947</v>
@@ -24914,14 +25016,14 @@
     </row>
     <row r="20" spans="1:30" ht="13">
       <c r="A20" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B20" s="6">
         <v>28237665854</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -24935,7 +25037,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="K20" s="8">
         <v>42947</v>
@@ -24948,7 +25050,7 @@
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
@@ -24968,14 +25070,14 @@
     </row>
     <row r="21" spans="1:30" ht="13">
       <c r="A21" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B21" s="6">
         <v>8707138958</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -24987,7 +25089,7 @@
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K21" s="8">
         <v>42947</v>
@@ -25018,16 +25120,16 @@
     </row>
     <row r="22" spans="1:30" ht="13">
       <c r="A22" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B22" s="6">
         <v>28744348718</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>551</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>552</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -25039,7 +25141,7 @@
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="67">
@@ -25068,16 +25170,16 @@
     </row>
     <row r="23" spans="1:30" ht="13">
       <c r="A23" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B23" s="6">
         <v>36888102974</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>554</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>555</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -25089,7 +25191,7 @@
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="67">
@@ -25118,14 +25220,14 @@
     </row>
     <row r="24" spans="1:30" ht="13">
       <c r="A24" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B24" s="6">
         <v>24430024334</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -25137,7 +25239,7 @@
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="7" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="K24" s="8">
         <v>42947</v>
@@ -25168,14 +25270,14 @@
     </row>
     <row r="25" spans="1:30" ht="13">
       <c r="A25" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B25" s="6">
         <v>2541268622</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -25187,7 +25289,7 @@
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K25" s="8">
         <v>42947</v>
@@ -25218,14 +25320,14 @@
     </row>
     <row r="26" spans="1:30" ht="13">
       <c r="A26" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B26" s="6">
         <v>11025043022</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -25237,7 +25339,7 @@
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K26" s="8">
         <v>43320</v>
@@ -25268,14 +25370,14 @@
     </row>
     <row r="27" spans="1:30" ht="13">
       <c r="A27" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B27" s="6">
         <v>35191276094</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -25287,7 +25389,7 @@
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K27" s="8">
         <v>42948</v>
@@ -25318,14 +25420,14 @@
     </row>
     <row r="28" spans="1:30" ht="13">
       <c r="A28" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B28" s="6">
         <v>41782089278</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -25337,7 +25439,7 @@
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K28" s="8">
         <v>42947</v>
@@ -25368,14 +25470,14 @@
     </row>
     <row r="29" spans="1:30" ht="13">
       <c r="A29" s="70" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B29" s="71">
         <v>41499995726</v>
       </c>
       <c r="C29" s="70"/>
       <c r="D29" s="70" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
@@ -25387,7 +25489,7 @@
       </c>
       <c r="I29" s="70"/>
       <c r="J29" s="72" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K29" s="73">
         <v>43320</v>
@@ -25418,14 +25520,14 @@
     </row>
     <row r="30" spans="1:30" ht="13">
       <c r="A30" s="70" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B30" s="71">
         <v>160678333382</v>
       </c>
       <c r="C30" s="70"/>
       <c r="D30" s="70" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -25435,7 +25537,7 @@
       <c r="H30" s="70"/>
       <c r="I30" s="70"/>
       <c r="J30" s="77" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K30" s="73">
         <v>43296</v>
@@ -25466,14 +25568,14 @@
     </row>
     <row r="31" spans="1:30" ht="13">
       <c r="A31" s="70" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B31" s="71">
         <v>36827636798</v>
       </c>
       <c r="C31" s="70"/>
       <c r="D31" s="70" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E31" s="70"/>
       <c r="F31" s="70"/>
@@ -25485,7 +25587,7 @@
       </c>
       <c r="I31" s="70"/>
       <c r="J31" s="77" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K31" s="70"/>
       <c r="L31" s="74">
@@ -25514,14 +25616,14 @@
     </row>
     <row r="32" spans="1:30" ht="13">
       <c r="A32" s="70" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B32" s="71">
         <v>36948569150</v>
       </c>
       <c r="C32" s="70"/>
       <c r="D32" s="70" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E32" s="70"/>
       <c r="F32" s="70"/>
@@ -25533,7 +25635,7 @@
       </c>
       <c r="I32" s="78"/>
       <c r="J32" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K32" s="70"/>
       <c r="L32" s="74">
@@ -25562,26 +25664,26 @@
     </row>
     <row r="33" spans="1:30" ht="13">
       <c r="A33" s="29" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C33" s="29"/>
       <c r="D33" s="29" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E33" s="29"/>
       <c r="F33" s="29"/>
       <c r="G33" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H33" s="29"/>
       <c r="I33" s="29" t="s">
         <v>20</v>
       </c>
       <c r="J33" s="31" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K33" s="35">
         <v>43208</v>
@@ -25610,26 +25712,26 @@
     </row>
     <row r="34" spans="1:30" ht="13">
       <c r="A34" s="79" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B34" s="80" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C34" s="79"/>
       <c r="D34" s="79" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E34" s="79"/>
       <c r="F34" s="79"/>
       <c r="G34" s="79" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H34" s="79"/>
       <c r="I34" s="79" t="s">
+        <v>572</v>
+      </c>
+      <c r="J34" s="81" t="s">
         <v>573</v>
-      </c>
-      <c r="J34" s="81" t="s">
-        <v>574</v>
       </c>
       <c r="K34" s="79"/>
       <c r="L34" s="79"/>
@@ -25654,26 +25756,26 @@
     </row>
     <row r="35" spans="1:30" ht="13">
       <c r="A35" s="79" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B35" s="80" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C35" s="79"/>
       <c r="D35" s="79" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E35" s="79"/>
       <c r="F35" s="79"/>
       <c r="G35" s="79" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H35" s="79"/>
       <c r="I35" s="79" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J35" s="81" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K35" s="79"/>
       <c r="L35" s="79"/>
@@ -25698,26 +25800,26 @@
     </row>
     <row r="36" spans="1:30" ht="13">
       <c r="A36" s="79" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B36" s="80" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C36" s="79"/>
       <c r="D36" s="79" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E36" s="79"/>
       <c r="F36" s="79"/>
       <c r="G36" s="79" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H36" s="79"/>
       <c r="I36" s="79" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J36" s="81" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K36" s="79"/>
       <c r="L36" s="79"/>
@@ -25742,26 +25844,26 @@
     </row>
     <row r="37" spans="1:30" ht="13">
       <c r="A37" s="79" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B37" s="80" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C37" s="79"/>
       <c r="D37" s="79" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E37" s="79"/>
       <c r="F37" s="79"/>
       <c r="G37" s="79" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H37" s="79"/>
       <c r="I37" s="79" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J37" s="81" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K37" s="79"/>
       <c r="L37" s="79"/>
@@ -25786,26 +25888,26 @@
     </row>
     <row r="38" spans="1:30" ht="13">
       <c r="A38" s="79" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C38" s="79"/>
       <c r="D38" s="79" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E38" s="79"/>
       <c r="F38" s="79"/>
       <c r="G38" s="79" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H38" s="79"/>
       <c r="I38" s="79" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J38" s="81" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K38" s="79"/>
       <c r="L38" s="79"/>
@@ -25830,26 +25932,26 @@
     </row>
     <row r="39" spans="1:30" ht="13">
       <c r="A39" s="79" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B39" s="80" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C39" s="79"/>
       <c r="D39" s="79" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E39" s="79"/>
       <c r="F39" s="79"/>
       <c r="G39" s="79" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H39" s="79"/>
       <c r="I39" s="79" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J39" s="81" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="K39" s="79"/>
       <c r="L39" s="79"/>
@@ -25874,26 +25976,26 @@
     </row>
     <row r="40" spans="1:30" ht="13">
       <c r="A40" s="82" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B40" s="71" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C40" s="82"/>
       <c r="D40" s="82" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E40" s="82"/>
       <c r="F40" s="82"/>
       <c r="G40" s="82" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H40" s="82"/>
       <c r="I40" s="82" t="s">
+        <v>592</v>
+      </c>
+      <c r="J40" s="83" t="s">
         <v>593</v>
-      </c>
-      <c r="J40" s="83" t="s">
-        <v>594</v>
       </c>
       <c r="K40" s="70"/>
       <c r="L40" s="70"/>
@@ -25920,28 +26022,28 @@
     </row>
     <row r="41" spans="1:30" ht="13">
       <c r="A41" s="82" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B41" s="71" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C41" s="82"/>
       <c r="D41" s="82" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
       <c r="G41" s="82" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H41" s="82" t="s">
+        <v>596</v>
+      </c>
+      <c r="I41" s="82" t="s">
         <v>597</v>
       </c>
-      <c r="I41" s="82" t="s">
+      <c r="J41" s="83" t="s">
         <v>598</v>
-      </c>
-      <c r="J41" s="83" t="s">
-        <v>599</v>
       </c>
       <c r="K41" s="84">
         <v>43208</v>
@@ -25970,28 +26072,28 @@
     </row>
     <row r="42" spans="1:30" ht="13">
       <c r="A42" s="82" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B42" s="71" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C42" s="82"/>
       <c r="D42" s="82" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E42" s="82"/>
       <c r="F42" s="82"/>
       <c r="G42" s="82" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H42" s="82" t="s">
+        <v>601</v>
+      </c>
+      <c r="I42" s="82" t="s">
         <v>602</v>
       </c>
-      <c r="I42" s="82" t="s">
+      <c r="J42" s="83" t="s">
         <v>603</v>
-      </c>
-      <c r="J42" s="83" t="s">
-        <v>604</v>
       </c>
       <c r="K42" s="84">
         <v>43208</v>
@@ -26020,26 +26122,26 @@
     </row>
     <row r="43" spans="1:30" ht="13">
       <c r="A43" s="82" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B43" s="71" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C43" s="82"/>
       <c r="D43" s="82" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E43" s="82"/>
       <c r="F43" s="82"/>
       <c r="G43" s="82" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H43" s="82" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I43" s="82"/>
       <c r="J43" s="83" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K43" s="84"/>
       <c r="L43" s="70"/>
@@ -26066,24 +26168,24 @@
     </row>
     <row r="44" spans="1:30" ht="13">
       <c r="A44" s="82" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B44" s="71" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C44" s="82"/>
       <c r="D44" s="82" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E44" s="82"/>
       <c r="F44" s="82"/>
       <c r="G44" s="82" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H44" s="82"/>
       <c r="I44" s="82"/>
       <c r="J44" s="83" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K44" s="70"/>
       <c r="L44" s="70"/>
@@ -26108,26 +26210,26 @@
     </row>
     <row r="45" spans="1:30" ht="13">
       <c r="A45" s="82" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B45" s="71" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C45" s="82"/>
       <c r="D45" s="82" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E45" s="82"/>
       <c r="F45" s="82"/>
       <c r="G45" s="82" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H45" s="82" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="I45" s="82"/>
       <c r="J45" s="83" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K45" s="84">
         <v>43208</v>
@@ -26154,26 +26256,26 @@
     </row>
     <row r="46" spans="1:30" ht="13">
       <c r="A46" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B46" s="86" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C46" s="85"/>
       <c r="D46" s="85" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E46" s="85"/>
       <c r="F46" s="85"/>
       <c r="G46" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H46" s="85"/>
       <c r="I46" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J46" s="87" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="K46" s="88"/>
       <c r="L46" s="89">
@@ -26202,26 +26304,26 @@
     </row>
     <row r="47" spans="1:30" ht="13">
       <c r="A47" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B47" s="86" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C47" s="85"/>
       <c r="D47" s="85" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E47" s="85"/>
       <c r="F47" s="85"/>
       <c r="G47" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H47" s="85"/>
       <c r="I47" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J47" s="87" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="K47" s="88"/>
       <c r="L47" s="89">
@@ -26248,26 +26350,26 @@
     </row>
     <row r="48" spans="1:30" ht="13">
       <c r="A48" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B48" s="86" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C48" s="85"/>
       <c r="D48" s="85" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E48" s="85"/>
       <c r="F48" s="85"/>
       <c r="G48" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H48" s="85"/>
       <c r="I48" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J48" s="87" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K48" s="88"/>
       <c r="L48" s="89">
@@ -26294,26 +26396,26 @@
     </row>
     <row r="49" spans="1:30" ht="13">
       <c r="A49" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B49" s="86" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C49" s="85"/>
       <c r="D49" s="85" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E49" s="85"/>
       <c r="F49" s="85"/>
       <c r="G49" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H49" s="85"/>
       <c r="I49" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J49" s="87" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="K49" s="88"/>
       <c r="L49" s="89">
@@ -26340,26 +26442,26 @@
     </row>
     <row r="50" spans="1:30" ht="13">
       <c r="A50" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B50" s="86" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C50" s="85"/>
       <c r="D50" s="85" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E50" s="85"/>
       <c r="F50" s="85"/>
       <c r="G50" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H50" s="85"/>
       <c r="I50" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J50" s="87" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="K50" s="88"/>
       <c r="L50" s="89">
@@ -26386,26 +26488,26 @@
     </row>
     <row r="51" spans="1:30" ht="13">
       <c r="A51" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B51" s="86" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C51" s="85"/>
       <c r="D51" s="85" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E51" s="85"/>
       <c r="F51" s="85"/>
       <c r="G51" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H51" s="85"/>
       <c r="I51" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J51" s="87" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="K51" s="88"/>
       <c r="L51" s="89">
@@ -26432,28 +26534,28 @@
     </row>
     <row r="52" spans="1:30" ht="13">
       <c r="A52" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B52" s="86" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C52" s="85"/>
       <c r="D52" s="85" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E52" s="85"/>
       <c r="F52" s="85"/>
       <c r="G52" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H52" s="85" t="s">
+        <v>636</v>
+      </c>
+      <c r="I52" s="85" t="s">
+        <v>250</v>
+      </c>
+      <c r="J52" s="87" t="s">
         <v>637</v>
-      </c>
-      <c r="I52" s="85" t="s">
-        <v>251</v>
-      </c>
-      <c r="J52" s="87" t="s">
-        <v>638</v>
       </c>
       <c r="K52" s="88"/>
       <c r="L52" s="89">
@@ -26480,26 +26582,26 @@
     </row>
     <row r="53" spans="1:30" ht="13">
       <c r="A53" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B53" s="86" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C53" s="85"/>
       <c r="D53" s="85" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E53" s="85"/>
       <c r="F53" s="85"/>
       <c r="G53" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H53" s="85"/>
       <c r="I53" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J53" s="87" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K53" s="88"/>
       <c r="L53" s="89">
@@ -26526,26 +26628,26 @@
     </row>
     <row r="54" spans="1:30" ht="13">
       <c r="A54" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B54" s="86" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C54" s="85"/>
       <c r="D54" s="85" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E54" s="85"/>
       <c r="F54" s="85"/>
       <c r="G54" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H54" s="85"/>
       <c r="I54" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J54" s="87" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="K54" s="88"/>
       <c r="L54" s="89">
@@ -26572,26 +26674,26 @@
     </row>
     <row r="55" spans="1:30" ht="13">
       <c r="A55" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B55" s="86" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C55" s="85"/>
       <c r="D55" s="85" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E55" s="85"/>
       <c r="F55" s="85"/>
       <c r="G55" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H55" s="85"/>
       <c r="I55" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J55" s="87" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="K55" s="88"/>
       <c r="L55" s="89">
@@ -26618,26 +26720,26 @@
     </row>
     <row r="56" spans="1:30" ht="13">
       <c r="A56" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B56" s="86" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C56" s="85"/>
       <c r="D56" s="85" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E56" s="85"/>
       <c r="F56" s="85"/>
       <c r="G56" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H56" s="85"/>
       <c r="I56" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J56" s="87" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="K56" s="88"/>
       <c r="L56" s="89">
@@ -26664,26 +26766,26 @@
     </row>
     <row r="57" spans="1:30" ht="13">
       <c r="A57" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B57" s="86" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C57" s="85"/>
       <c r="D57" s="85" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E57" s="85"/>
       <c r="F57" s="85"/>
       <c r="G57" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H57" s="85"/>
       <c r="I57" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J57" s="87" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K57" s="88"/>
       <c r="L57" s="89">
@@ -26710,26 +26812,26 @@
     </row>
     <row r="58" spans="1:30" ht="6.75" customHeight="1">
       <c r="A58" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B58" s="86" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C58" s="85"/>
       <c r="D58" s="85" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E58" s="85"/>
       <c r="F58" s="85"/>
       <c r="G58" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H58" s="85"/>
       <c r="I58" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J58" s="87" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="K58" s="88"/>
       <c r="L58" s="89">
@@ -26756,26 +26858,26 @@
     </row>
     <row r="59" spans="1:30" ht="18.75" customHeight="1">
       <c r="A59" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B59" s="86" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C59" s="85"/>
       <c r="D59" s="85" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E59" s="85"/>
       <c r="F59" s="85"/>
       <c r="G59" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H59" s="85"/>
       <c r="I59" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J59" s="87" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K59" s="88"/>
       <c r="L59" s="89">
@@ -26802,26 +26904,26 @@
     </row>
     <row r="60" spans="1:30" ht="18.75" customHeight="1">
       <c r="A60" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B60" s="86" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C60" s="85"/>
       <c r="D60" s="85" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E60" s="85"/>
       <c r="F60" s="85"/>
       <c r="G60" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H60" s="85"/>
       <c r="I60" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J60" s="87" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K60" s="88"/>
       <c r="L60" s="89">
@@ -26848,26 +26950,26 @@
     </row>
     <row r="61" spans="1:30" ht="19.5" customHeight="1">
       <c r="A61" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B61" s="86" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C61" s="85"/>
       <c r="D61" s="85" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E61" s="85"/>
       <c r="F61" s="85"/>
       <c r="G61" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H61" s="85"/>
       <c r="I61" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J61" s="87" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K61" s="88"/>
       <c r="L61" s="89">
@@ -26894,26 +26996,26 @@
     </row>
     <row r="62" spans="1:30" ht="19.5" customHeight="1">
       <c r="A62" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B62" s="86" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C62" s="85"/>
       <c r="D62" s="85" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E62" s="85"/>
       <c r="F62" s="85"/>
       <c r="G62" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H62" s="85"/>
       <c r="I62" s="85" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J62" s="87" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K62" s="88"/>
       <c r="L62" s="89">
@@ -26940,26 +27042,26 @@
     </row>
     <row r="63" spans="1:30" ht="19.5" customHeight="1">
       <c r="A63" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B63" s="86" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C63" s="85"/>
       <c r="D63" s="85" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E63" s="85"/>
       <c r="F63" s="85"/>
       <c r="G63" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H63" s="85"/>
       <c r="I63" s="85" t="s">
         <v>20</v>
       </c>
       <c r="J63" s="87" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="K63" s="88"/>
       <c r="L63" s="89">
@@ -26988,26 +27090,26 @@
     </row>
     <row r="64" spans="1:30" ht="19.5" customHeight="1">
       <c r="A64" s="85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B64" s="86" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C64" s="85"/>
       <c r="D64" s="85" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E64" s="85"/>
       <c r="F64" s="85"/>
       <c r="G64" s="85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H64" s="85" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="I64" s="85"/>
       <c r="J64" s="87" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="K64" s="90">
         <v>43407</v>
@@ -27017,7 +27119,7 @@
         <v>45406</v>
       </c>
       <c r="N64" s="88" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="O64" s="88"/>
       <c r="P64" s="88"/>
@@ -27038,28 +27140,28 @@
     </row>
     <row r="65" spans="1:30" ht="19.5" customHeight="1">
       <c r="A65" s="91" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B65" s="92" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C65" s="91"/>
       <c r="D65" s="91" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E65" s="91"/>
       <c r="F65" s="91"/>
       <c r="G65" s="91" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H65" s="91" t="s">
         <v>19</v>
       </c>
       <c r="I65" s="91" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J65" s="93" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="K65" s="94">
         <v>43076</v>
@@ -27090,28 +27192,28 @@
     </row>
     <row r="66" spans="1:30" ht="9" customHeight="1">
       <c r="A66" s="91" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B66" s="92" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C66" s="91"/>
       <c r="D66" s="91" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E66" s="91"/>
       <c r="F66" s="91"/>
       <c r="G66" s="91" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H66" s="91" t="s">
         <v>19</v>
       </c>
       <c r="I66" s="91" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J66" s="93" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K66" s="94">
         <v>43076</v>
@@ -27142,19 +27244,19 @@
     </row>
     <row r="67" spans="1:30" ht="13">
       <c r="A67" s="95" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B67" s="96" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C67" s="95"/>
       <c r="D67" s="95" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E67" s="95"/>
       <c r="F67" s="95"/>
       <c r="G67" s="95" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H67" s="95"/>
       <c r="I67" s="95" t="s">
@@ -27186,14 +27288,14 @@
     </row>
     <row r="68" spans="1:30" ht="13">
       <c r="A68" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C68" s="14"/>
       <c r="D68" s="14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E68" s="14"/>
       <c r="F68" s="14"/>
@@ -27234,14 +27336,14 @@
     </row>
     <row r="69" spans="1:30" ht="13">
       <c r="A69" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C69" s="14"/>
       <c r="D69" s="14" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E69" s="14"/>
       <c r="F69" s="14"/>
@@ -27282,14 +27384,14 @@
     </row>
     <row r="70" spans="1:30" ht="13">
       <c r="A70" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E70" s="14"/>
       <c r="F70" s="14"/>
